--- a/extenbooks/S1603_extenbook.xlsx
+++ b/extenbooks/S1603_extenbook.xlsx
@@ -4408,7 +4408,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -5880,11 +5880,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5907,76 +5907,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>US and OECD Short-Term Interest Rates</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension_deferred", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1603_research.json", "adequacy_report": "Technical/docs/chapters/CH16_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1603_DPR.md", "epr": "Technical/docs/series/S1603_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1603_load.py", "processor": "Technical/code/P02_processors/P02_S1603_construct.py", "validator": "Technical/code/V03_validators/V03_S1603_validate.py", "processed": "Technical/data/processed/S1603.parquet", "chopped_csv": "Technical/chopped/S1603.csv", "extenbook_xlsx": "Technical/extenbooks/S1603_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-19T00:17:23.977169+00:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1603_extenbook.xlsx
+++ b/extenbooks/S1603_extenbook.xlsx
@@ -649,13 +649,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E186"/>
+  <dimension ref="A1:E185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="57" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -694,7 +694,7 @@
         <v>1960</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0411667</v>
+        <v>0.02928</v>
       </c>
       <c r="C4" t="n">
         <v>0.04913350440729029</v>
@@ -708,7 +708,7 @@
         <v>1961</v>
       </c>
       <c r="B5" t="n">
-        <v>0.038825</v>
+        <v>0.02378</v>
       </c>
       <c r="C5" t="n">
         <v>0.04638770654060418</v>
@@ -722,7 +722,7 @@
         <v>1962</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0394583</v>
+        <v>0.02778</v>
       </c>
       <c r="C6" t="n">
         <v>0.04543594789165934</v>
@@ -736,7 +736,7 @@
         <v>1963</v>
       </c>
       <c r="B7" t="n">
-        <v>0.04002500000000001</v>
+        <v>0.03157</v>
       </c>
       <c r="C7" t="n">
         <v>0.04603669115050479</v>
@@ -750,7 +750,7 @@
         <v>1964</v>
       </c>
       <c r="B8" t="n">
-        <v>0.04186670000000001</v>
+        <v>0.03549</v>
       </c>
       <c r="C8" t="n">
         <v>0.0496307782583563</v>
@@ -764,7 +764,7 @@
         <v>1965</v>
       </c>
       <c r="B9" t="n">
-        <v>0.04344166999999999</v>
+        <v>0.03954</v>
       </c>
       <c r="C9" t="n">
         <v>0.05461605969216875</v>
@@ -778,7 +778,7 @@
         <v>1966</v>
       </c>
       <c r="B10" t="n">
-        <v>0.05483333</v>
+        <v>0.04881</v>
       </c>
       <c r="C10" t="n">
         <v>0.06225500588928039</v>
@@ -792,7 +792,7 @@
         <v>1967</v>
       </c>
       <c r="B11" t="n">
-        <v>0.05020833</v>
+        <v>0.04321</v>
       </c>
       <c r="C11" t="n">
         <v>0.05702860156467568</v>
@@ -806,7 +806,7 @@
         <v>1968</v>
       </c>
       <c r="B12" t="n">
-        <v>0.05859167000000001</v>
+        <v>0.05339000000000001</v>
       </c>
       <c r="C12" t="n">
         <v>0.0593073833616693</v>
@@ -820,7 +820,7 @@
         <v>1969</v>
       </c>
       <c r="B13" t="n">
-        <v>0.07760833</v>
+        <v>0.06677</v>
       </c>
       <c r="C13" t="n">
         <v>0.07253099604577662</v>
@@ -834,7 +834,7 @@
         <v>1970</v>
       </c>
       <c r="B14" t="n">
-        <v>0.07564167000000001</v>
+        <v>0.06458</v>
       </c>
       <c r="C14" t="n">
         <v>0.08078753473709199</v>
@@ -848,7 +848,7 @@
         <v>1971</v>
       </c>
       <c r="B15" t="n">
-        <v>0.05005</v>
+        <v>0.04348</v>
       </c>
       <c r="C15" t="n">
         <v>0.0635912064916753</v>
@@ -862,7 +862,7 @@
         <v>1972</v>
       </c>
       <c r="B16" t="n">
-        <v>0.04665833</v>
+        <v>0.04071</v>
       </c>
       <c r="C16" t="n">
         <v>0.05827972146452961</v>
@@ -876,7 +876,7 @@
         <v>1973</v>
       </c>
       <c r="B17" t="n">
-        <v>0.08415832999999999</v>
+        <v>0.07041</v>
       </c>
       <c r="C17" t="n">
         <v>0.08625426774001994</v>
@@ -890,7 +890,7 @@
         <v>1974</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1024417</v>
+        <v>0.07886</v>
       </c>
       <c r="C18" t="n">
         <v>0.1042277738186976</v>
@@ -904,7 +904,7 @@
         <v>1975</v>
       </c>
       <c r="B19" t="n">
-        <v>0.06436665999999999</v>
+        <v>0.05838</v>
       </c>
       <c r="C19" t="n">
         <v>0.07686079814214808</v>
@@ -918,7 +918,7 @@
         <v>1976</v>
       </c>
       <c r="B20" t="n">
-        <v>0.05268333</v>
+        <v>0.04989</v>
       </c>
       <c r="C20" t="n">
         <v>0.07701920879562994</v>
@@ -932,7 +932,7 @@
         <v>1977</v>
       </c>
       <c r="B21" t="n">
-        <v>0.05640833</v>
+        <v>0.05265</v>
       </c>
       <c r="C21" t="n">
         <v>0.07438839813427206</v>
@@ -946,7 +946,7 @@
         <v>1978</v>
       </c>
       <c r="B22" t="n">
-        <v>0.08221666000000001</v>
+        <v>0.07221</v>
       </c>
       <c r="C22" t="n">
         <v>0.07735293431432522</v>
@@ -960,7 +960,7 @@
         <v>1979</v>
       </c>
       <c r="B23" t="n">
-        <v>0.11225</v>
+        <v>0.10041</v>
       </c>
       <c r="C23" t="n">
         <v>0.09939643216740328</v>
@@ -974,7 +974,7 @@
         <v>1980</v>
       </c>
       <c r="B24" t="n">
-        <v>0.1306667</v>
+        <v>0.11506</v>
       </c>
       <c r="C24" t="n">
         <v>0.1200518199734605</v>
@@ -988,7 +988,7 @@
         <v>1981</v>
       </c>
       <c r="B25" t="n">
-        <v>0.1591083</v>
+        <v>0.14029</v>
       </c>
       <c r="C25" t="n">
         <v>0.1393095382041335</v>
@@ -1002,7 +1002,7 @@
         <v>1982</v>
       </c>
       <c r="B26" t="n">
-        <v>0.1227083</v>
+        <v>0.10686</v>
       </c>
       <c r="C26" t="n">
         <v>0.1193240301927182</v>
@@ -1016,7 +1016,7 @@
         <v>1983</v>
       </c>
       <c r="B27" t="n">
-        <v>0.09066667</v>
+        <v>0.0863</v>
       </c>
       <c r="C27" t="n">
         <v>0.09505872266825782</v>
@@ -1030,7 +1030,7 @@
         <v>1984</v>
       </c>
       <c r="B28" t="n">
-        <v>0.10365</v>
+        <v>0.0958</v>
       </c>
       <c r="C28" t="n">
         <v>0.09736355101129524</v>
@@ -1044,7 +1044,7 @@
         <v>1985</v>
       </c>
       <c r="B29" t="n">
-        <v>0.08047499999999999</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="C29" t="n">
         <v>0.08588176626890473</v>
@@ -1058,7 +1058,7 @@
         <v>1986</v>
       </c>
       <c r="B30" t="n">
-        <v>0.06518333</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="C30" t="n">
         <v>0.07205954294186155</v>
@@ -1072,7 +1072,7 @@
         <v>1987</v>
       </c>
       <c r="B31" t="n">
-        <v>0.06860833000000001</v>
+        <v>0.0582</v>
       </c>
       <c r="C31" t="n">
         <v>0.06944729702201671</v>
@@ -1086,7 +1086,7 @@
         <v>1988</v>
       </c>
       <c r="B32" t="n">
-        <v>0.077275</v>
+        <v>0.0669</v>
       </c>
       <c r="C32" t="n">
         <v>0.07212436288682611</v>
@@ -1100,7 +1100,7 @@
         <v>1989</v>
       </c>
       <c r="B33" t="n">
-        <v>0.09085000000000001</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="C33" t="n">
         <v>0.08802815504651956</v>
@@ -1114,7 +1114,7 @@
         <v>1990</v>
       </c>
       <c r="B34" t="n">
-        <v>0.08147500000000001</v>
+        <v>0.0751</v>
       </c>
       <c r="C34" t="n">
         <v>0.09635491586720331</v>
@@ -1128,7 +1128,7 @@
         <v>1991</v>
       </c>
       <c r="B35" t="n">
-        <v>0.05835</v>
+        <v>0.0542</v>
       </c>
       <c r="C35" t="n">
         <v>0.08581710861637996</v>
@@ -1142,7 +1142,7 @@
         <v>1992</v>
       </c>
       <c r="B36" t="n">
-        <v>0.03681667</v>
+        <v>0.0345</v>
       </c>
       <c r="C36" t="n">
         <v>0.07396279246697947</v>
@@ -1156,7 +1156,7 @@
         <v>1993</v>
       </c>
       <c r="B37" t="n">
-        <v>0.03174167</v>
+        <v>0.0302</v>
       </c>
       <c r="C37" t="n">
         <v>0.05713243419212476</v>
@@ -1170,7 +1170,7 @@
         <v>1994</v>
       </c>
       <c r="B38" t="n">
-        <v>0.04629167</v>
+        <v>0.0429</v>
       </c>
       <c r="C38" t="n">
         <v>0.05798942354624027</v>
@@ -1184,7 +1184,7 @@
         <v>1995</v>
       </c>
       <c r="B39" t="n">
-        <v>0.05916667</v>
+        <v>0.0551</v>
       </c>
       <c r="C39" t="n">
         <v>0.05940047156615028</v>
@@ -1198,7 +1198,7 @@
         <v>1996</v>
       </c>
       <c r="B40" t="n">
-        <v>0.0539</v>
+        <v>0.05019999999999999</v>
       </c>
       <c r="C40" t="n">
         <v>0.04778545532168525</v>
@@ -1212,7 +1212,7 @@
         <v>1997</v>
       </c>
       <c r="B41" t="n">
-        <v>0.05615833000000001</v>
+        <v>0.0507</v>
       </c>
       <c r="C41" t="n">
         <v>0.04443014677810425</v>
@@ -1226,7 +1226,7 @@
         <v>1998</v>
       </c>
       <c r="B42" t="n">
-        <v>0.05466667</v>
+        <v>0.0481</v>
       </c>
       <c r="C42" t="n">
         <v>0.04135209218690966</v>
@@ -1240,7 +1240,7 @@
         <v>1999</v>
       </c>
       <c r="B43" t="n">
-        <v>0.0533</v>
+        <v>0.0466</v>
       </c>
       <c r="C43" t="n">
         <v>0.03951014721964399</v>
@@ -1254,7 +1254,7 @@
         <v>2000</v>
       </c>
       <c r="B44" t="n">
-        <v>0.06455833</v>
+        <v>0.0585</v>
       </c>
       <c r="C44" t="n">
         <v>0.04876478256448426</v>
@@ -1268,7 +1268,7 @@
         <v>2001</v>
       </c>
       <c r="B45" t="n">
-        <v>0.03686667</v>
+        <v>0.0345</v>
       </c>
       <c r="C45" t="n">
         <v>0.03868876360749711</v>
@@ -1282,7 +1282,7 @@
         <v>2002</v>
       </c>
       <c r="B46" t="n">
-        <v>0.01725833</v>
+        <v>0.0162</v>
       </c>
       <c r="C46" t="n">
         <v>0.0289628430536128</v>
@@ -1296,7 +1296,7 @@
         <v>2003</v>
       </c>
       <c r="B47" t="n">
-        <v>0.01150833</v>
+        <v>0.0102</v>
       </c>
       <c r="C47" t="n">
         <v>0.02256549244834405</v>
@@ -1310,7 +1310,7 @@
         <v>2004</v>
       </c>
       <c r="B48" t="n">
-        <v>0.01563333</v>
+        <v>0.0138</v>
       </c>
       <c r="C48" t="n">
         <v>0.02409742001832007</v>
@@ -1324,7 +1324,7 @@
         <v>2005</v>
       </c>
       <c r="B49" t="n">
-        <v>0.03511667</v>
+        <v>0.0316</v>
       </c>
       <c r="C49" t="n">
         <v>0.02783040091768195</v>
@@ -1338,7 +1338,7 @@
         <v>2006</v>
       </c>
       <c r="B50" t="n">
-        <v>0.05153333</v>
+        <v>0.0473</v>
       </c>
       <c r="C50" t="n">
         <v>0.03657379469833752</v>
@@ -1352,7 +1352,7 @@
         <v>2007</v>
       </c>
       <c r="B51" t="n">
-        <v>0.05268333</v>
+        <v>0.0441</v>
       </c>
       <c r="C51" t="n">
         <v>0.04230796637396485</v>
@@ -1366,7 +1366,7 @@
         <v>2008</v>
       </c>
       <c r="B52" t="n">
-        <v>0.02965</v>
+        <v>0.0148</v>
       </c>
       <c r="C52" t="n">
         <v>0.03649718194451612</v>
@@ -1380,7 +1380,7 @@
         <v>2009</v>
       </c>
       <c r="B53" t="n">
-        <v>0.005558333</v>
+        <v>0.0016</v>
       </c>
       <c r="C53" t="n">
         <v>0.01360642875451092</v>
@@ -1394,7 +1394,7 @@
         <v>2010</v>
       </c>
       <c r="B54" t="n">
-        <v>0.0031</v>
+        <v>0.0014</v>
       </c>
       <c r="C54" t="n">
         <v>0.00896033113101939</v>
@@ -1408,7 +1408,7 @@
         <v>2011</v>
       </c>
       <c r="B55" t="n">
-        <v>0.003</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="C55" t="n">
         <v>0.01537637070631722</v>
@@ -1422,7 +1422,7 @@
         <v>2012</v>
       </c>
       <c r="B56" t="n">
-        <v>0.0028</v>
+        <v/>
       </c>
       <c r="C56" t="n">
         <v>0.00630541820330994</v>
@@ -1473,7 +1473,7 @@
         <v>1960</v>
       </c>
       <c r="B62" t="n">
-        <v>0.0411667</v>
+        <v>0.02928</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -1496,7 +1496,7 @@
         <v>1961</v>
       </c>
       <c r="B63" t="n">
-        <v>0.038825</v>
+        <v>0.02378</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -1519,7 +1519,7 @@
         <v>1962</v>
       </c>
       <c r="B64" t="n">
-        <v>0.0394583</v>
+        <v>0.02778</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -1542,7 +1542,7 @@
         <v>1963</v>
       </c>
       <c r="B65" t="n">
-        <v>0.04002500000000001</v>
+        <v>0.03157</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -1565,7 +1565,7 @@
         <v>1964</v>
       </c>
       <c r="B66" t="n">
-        <v>0.04186670000000001</v>
+        <v>0.03549</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -1588,7 +1588,7 @@
         <v>1965</v>
       </c>
       <c r="B67" t="n">
-        <v>0.04344166999999999</v>
+        <v>0.03954</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -1611,7 +1611,7 @@
         <v>1966</v>
       </c>
       <c r="B68" t="n">
-        <v>0.05483333</v>
+        <v>0.04881</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -1634,7 +1634,7 @@
         <v>1967</v>
       </c>
       <c r="B69" t="n">
-        <v>0.05020833</v>
+        <v>0.04321</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -1657,7 +1657,7 @@
         <v>1968</v>
       </c>
       <c r="B70" t="n">
-        <v>0.05859167000000001</v>
+        <v>0.05339000000000001</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -1680,7 +1680,7 @@
         <v>1969</v>
       </c>
       <c r="B71" t="n">
-        <v>0.07760833</v>
+        <v>0.06677</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -1703,7 +1703,7 @@
         <v>1970</v>
       </c>
       <c r="B72" t="n">
-        <v>0.07564167000000001</v>
+        <v>0.06458</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -1726,7 +1726,7 @@
         <v>1971</v>
       </c>
       <c r="B73" t="n">
-        <v>0.05005</v>
+        <v>0.04348</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -1749,7 +1749,7 @@
         <v>1972</v>
       </c>
       <c r="B74" t="n">
-        <v>0.04665833</v>
+        <v>0.04071</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -1772,7 +1772,7 @@
         <v>1973</v>
       </c>
       <c r="B75" t="n">
-        <v>0.08415832999999999</v>
+        <v>0.07041</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -1795,7 +1795,7 @@
         <v>1974</v>
       </c>
       <c r="B76" t="n">
-        <v>0.1024417</v>
+        <v>0.07886</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -1818,7 +1818,7 @@
         <v>1975</v>
       </c>
       <c r="B77" t="n">
-        <v>0.06436665999999999</v>
+        <v>0.05838</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -1841,7 +1841,7 @@
         <v>1976</v>
       </c>
       <c r="B78" t="n">
-        <v>0.05268333</v>
+        <v>0.04989</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -1864,7 +1864,7 @@
         <v>1977</v>
       </c>
       <c r="B79" t="n">
-        <v>0.05640833</v>
+        <v>0.05265</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -1887,7 +1887,7 @@
         <v>1978</v>
       </c>
       <c r="B80" t="n">
-        <v>0.08221666000000001</v>
+        <v>0.07221</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -1910,7 +1910,7 @@
         <v>1979</v>
       </c>
       <c r="B81" t="n">
-        <v>0.11225</v>
+        <v>0.10041</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -1933,7 +1933,7 @@
         <v>1980</v>
       </c>
       <c r="B82" t="n">
-        <v>0.1306667</v>
+        <v>0.11506</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -1956,7 +1956,7 @@
         <v>1981</v>
       </c>
       <c r="B83" t="n">
-        <v>0.1591083</v>
+        <v>0.14029</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -1979,7 +1979,7 @@
         <v>1982</v>
       </c>
       <c r="B84" t="n">
-        <v>0.1227083</v>
+        <v>0.10686</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2002,7 +2002,7 @@
         <v>1983</v>
       </c>
       <c r="B85" t="n">
-        <v>0.09066667</v>
+        <v>0.0863</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2025,7 +2025,7 @@
         <v>1984</v>
       </c>
       <c r="B86" t="n">
-        <v>0.10365</v>
+        <v>0.0958</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2048,7 +2048,7 @@
         <v>1985</v>
       </c>
       <c r="B87" t="n">
-        <v>0.08047499999999999</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2071,7 +2071,7 @@
         <v>1986</v>
       </c>
       <c r="B88" t="n">
-        <v>0.06518333</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -2094,7 +2094,7 @@
         <v>1987</v>
       </c>
       <c r="B89" t="n">
-        <v>0.06860833000000001</v>
+        <v>0.0582</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -2117,7 +2117,7 @@
         <v>1988</v>
       </c>
       <c r="B90" t="n">
-        <v>0.077275</v>
+        <v>0.0669</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -2140,7 +2140,7 @@
         <v>1989</v>
       </c>
       <c r="B91" t="n">
-        <v>0.09085000000000001</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -2163,7 +2163,7 @@
         <v>1990</v>
       </c>
       <c r="B92" t="n">
-        <v>0.08147500000000001</v>
+        <v>0.0751</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -2186,7 +2186,7 @@
         <v>1991</v>
       </c>
       <c r="B93" t="n">
-        <v>0.05835</v>
+        <v>0.0542</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -2209,7 +2209,7 @@
         <v>1992</v>
       </c>
       <c r="B94" t="n">
-        <v>0.03681667</v>
+        <v>0.0345</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -2232,7 +2232,7 @@
         <v>1993</v>
       </c>
       <c r="B95" t="n">
-        <v>0.03174167</v>
+        <v>0.0302</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -2255,7 +2255,7 @@
         <v>1994</v>
       </c>
       <c r="B96" t="n">
-        <v>0.04629167</v>
+        <v>0.0429</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -2278,7 +2278,7 @@
         <v>1995</v>
       </c>
       <c r="B97" t="n">
-        <v>0.05916667</v>
+        <v>0.0551</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -2301,7 +2301,7 @@
         <v>1996</v>
       </c>
       <c r="B98" t="n">
-        <v>0.0539</v>
+        <v>0.05019999999999999</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -2324,7 +2324,7 @@
         <v>1997</v>
       </c>
       <c r="B99" t="n">
-        <v>0.05615833000000001</v>
+        <v>0.0507</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -2347,7 +2347,7 @@
         <v>1998</v>
       </c>
       <c r="B100" t="n">
-        <v>0.05466667</v>
+        <v>0.0481</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -2370,7 +2370,7 @@
         <v>1999</v>
       </c>
       <c r="B101" t="n">
-        <v>0.0533</v>
+        <v>0.0466</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -2393,7 +2393,7 @@
         <v>2000</v>
       </c>
       <c r="B102" t="n">
-        <v>0.06455833</v>
+        <v>0.0585</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -2416,7 +2416,7 @@
         <v>2001</v>
       </c>
       <c r="B103" t="n">
-        <v>0.03686667</v>
+        <v>0.0345</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -2439,7 +2439,7 @@
         <v>2002</v>
       </c>
       <c r="B104" t="n">
-        <v>0.01725833</v>
+        <v>0.0162</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -2462,7 +2462,7 @@
         <v>2003</v>
       </c>
       <c r="B105" t="n">
-        <v>0.01150833</v>
+        <v>0.0102</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -2485,7 +2485,7 @@
         <v>2004</v>
       </c>
       <c r="B106" t="n">
-        <v>0.01563333</v>
+        <v>0.0138</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -2508,7 +2508,7 @@
         <v>2005</v>
       </c>
       <c r="B107" t="n">
-        <v>0.03511667</v>
+        <v>0.0316</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -2531,7 +2531,7 @@
         <v>2006</v>
       </c>
       <c r="B108" t="n">
-        <v>0.05153333</v>
+        <v>0.0473</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -2554,7 +2554,7 @@
         <v>2007</v>
       </c>
       <c r="B109" t="n">
-        <v>0.05268333</v>
+        <v>0.0441</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -2577,7 +2577,7 @@
         <v>2008</v>
       </c>
       <c r="B110" t="n">
-        <v>0.02965</v>
+        <v>0.0148</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -2600,7 +2600,7 @@
         <v>2009</v>
       </c>
       <c r="B111" t="n">
-        <v>0.005558333</v>
+        <v>0.0016</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -2623,7 +2623,7 @@
         <v>2010</v>
       </c>
       <c r="B112" t="n">
-        <v>0.0031</v>
+        <v>0.0014</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -2646,7 +2646,7 @@
         <v>2011</v>
       </c>
       <c r="B113" t="n">
-        <v>0.003</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -2666,14 +2666,14 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>2012</v>
+        <v>1960</v>
       </c>
       <c r="B114" t="n">
-        <v>0.0028</v>
+        <v>0.04913350440729029</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>S1603-A</t>
+          <t>S1603-B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -2689,10 +2689,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="B115" t="n">
-        <v>0.04913350440729029</v>
+        <v>0.04638770654060418</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="B116" t="n">
-        <v>0.04638770654060418</v>
+        <v>0.04543594789165934</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="B117" t="n">
-        <v>0.04543594789165934</v>
+        <v>0.04603669115050479</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -2758,10 +2758,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="B118" t="n">
-        <v>0.04603669115050479</v>
+        <v>0.0496307782583563</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -2781,10 +2781,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="B119" t="n">
-        <v>0.0496307782583563</v>
+        <v>0.05461605969216875</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -2804,10 +2804,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="B120" t="n">
-        <v>0.05461605969216875</v>
+        <v>0.06225500588928039</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="B121" t="n">
-        <v>0.06225500588928039</v>
+        <v>0.05702860156467568</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -2850,10 +2850,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="B122" t="n">
-        <v>0.05702860156467568</v>
+        <v>0.0593073833616693</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -2873,10 +2873,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="B123" t="n">
-        <v>0.0593073833616693</v>
+        <v>0.07253099604577662</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="B124" t="n">
-        <v>0.07253099604577662</v>
+        <v>0.08078753473709199</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="B125" t="n">
-        <v>0.08078753473709199</v>
+        <v>0.0635912064916753</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="B126" t="n">
-        <v>0.0635912064916753</v>
+        <v>0.05827972146452961</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -2965,10 +2965,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="B127" t="n">
-        <v>0.05827972146452961</v>
+        <v>0.08625426774001994</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -2988,10 +2988,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="B128" t="n">
-        <v>0.08625426774001994</v>
+        <v>0.1042277738186976</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -3011,10 +3011,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="B129" t="n">
-        <v>0.1042277738186976</v>
+        <v>0.07686079814214808</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -3034,10 +3034,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="B130" t="n">
-        <v>0.07686079814214808</v>
+        <v>0.07701920879562994</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -3057,10 +3057,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="B131" t="n">
-        <v>0.07701920879562994</v>
+        <v>0.07438839813427206</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -3080,10 +3080,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="B132" t="n">
-        <v>0.07438839813427206</v>
+        <v>0.07735293431432522</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -3103,10 +3103,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="B133" t="n">
-        <v>0.07735293431432522</v>
+        <v>0.09939643216740328</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -3126,10 +3126,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="B134" t="n">
-        <v>0.09939643216740328</v>
+        <v>0.1200518199734605</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -3149,10 +3149,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="B135" t="n">
-        <v>0.1200518199734605</v>
+        <v>0.1393095382041335</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -3172,10 +3172,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="B136" t="n">
-        <v>0.1393095382041335</v>
+        <v>0.1193240301927182</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -3195,10 +3195,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="B137" t="n">
-        <v>0.1193240301927182</v>
+        <v>0.09505872266825782</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -3218,10 +3218,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="B138" t="n">
-        <v>0.09505872266825782</v>
+        <v>0.09736355101129524</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -3241,10 +3241,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="B139" t="n">
-        <v>0.09736355101129524</v>
+        <v>0.08588176626890473</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -3264,10 +3264,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="B140" t="n">
-        <v>0.08588176626890473</v>
+        <v>0.07205954294186155</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -3287,10 +3287,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="B141" t="n">
-        <v>0.07205954294186155</v>
+        <v>0.06944729702201671</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="B142" t="n">
-        <v>0.06944729702201671</v>
+        <v>0.07212436288682611</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -3333,10 +3333,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="B143" t="n">
-        <v>0.07212436288682611</v>
+        <v>0.08802815504651956</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="B144" t="n">
-        <v>0.08802815504651956</v>
+        <v>0.09635491586720331</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -3379,10 +3379,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="B145" t="n">
-        <v>0.09635491586720331</v>
+        <v>0.08581710861637996</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="B146" t="n">
-        <v>0.08581710861637996</v>
+        <v>0.07396279246697947</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -3425,10 +3425,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="B147" t="n">
-        <v>0.07396279246697947</v>
+        <v>0.05713243419212476</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -3448,10 +3448,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="B148" t="n">
-        <v>0.05713243419212476</v>
+        <v>0.05798942354624027</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -3471,10 +3471,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="B149" t="n">
-        <v>0.05798942354624027</v>
+        <v>0.05940047156615028</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="B150" t="n">
-        <v>0.05940047156615028</v>
+        <v>0.04778545532168525</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -3517,10 +3517,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="B151" t="n">
-        <v>0.04778545532168525</v>
+        <v>0.04443014677810425</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -3540,10 +3540,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="B152" t="n">
-        <v>0.04443014677810425</v>
+        <v>0.04135209218690966</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -3563,10 +3563,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="B153" t="n">
-        <v>0.04135209218690966</v>
+        <v>0.03951014721964399</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -3586,10 +3586,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="B154" t="n">
-        <v>0.03951014721964399</v>
+        <v>0.04876478256448426</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -3609,10 +3609,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="B155" t="n">
-        <v>0.04876478256448426</v>
+        <v>0.03868876360749711</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -3632,10 +3632,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="B156" t="n">
-        <v>0.03868876360749711</v>
+        <v>0.0289628430536128</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -3655,10 +3655,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B157" t="n">
-        <v>0.0289628430536128</v>
+        <v>0.02256549244834405</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -3678,10 +3678,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B158" t="n">
-        <v>0.02256549244834405</v>
+        <v>0.02409742001832007</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -3701,10 +3701,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B159" t="n">
-        <v>0.02409742001832007</v>
+        <v>0.02783040091768195</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -3724,10 +3724,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B160" t="n">
-        <v>0.02783040091768195</v>
+        <v>0.03657379469833752</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B161" t="n">
-        <v>0.03657379469833752</v>
+        <v>0.04230796637396485</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -3770,10 +3770,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B162" t="n">
-        <v>0.04230796637396485</v>
+        <v>0.03649718194451612</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B163" t="n">
-        <v>0.03649718194451612</v>
+        <v>0.01360642875451092</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B164" t="n">
-        <v>0.01360642875451092</v>
+        <v>0.00896033113101939</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -3839,10 +3839,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B165" t="n">
-        <v>0.00896033113101939</v>
+        <v>0.01537637070631722</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -3862,10 +3862,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B166" t="n">
-        <v>0.01537637070631722</v>
+        <v>0.00630541820330994</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -3885,14 +3885,14 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>2012</v>
+        <v>1994</v>
       </c>
       <c r="B167" t="n">
-        <v>0.00630541820330994</v>
+        <v>0.0653</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>S1603-B</t>
+          <t>S1603-C</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -3908,10 +3908,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="B168" t="n">
-        <v>0.0653</v>
+        <v>0.0682</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -3931,10 +3931,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="B169" t="n">
-        <v>0.0682</v>
+        <v>0.0509</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -3954,10 +3954,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="B170" t="n">
-        <v>0.0509</v>
+        <v>0.0438</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -3977,10 +3977,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="B171" t="n">
-        <v>0.0438</v>
+        <v>0.0396</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -4000,10 +4000,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="B172" t="n">
-        <v>0.0396</v>
+        <v>0.0296</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -4023,10 +4023,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="B173" t="n">
-        <v>0.0296</v>
+        <v>0.04389999999999999</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -4046,10 +4046,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="B174" t="n">
-        <v>0.04389999999999999</v>
+        <v>0.0426</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -4069,10 +4069,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="B175" t="n">
-        <v>0.0426</v>
+        <v>0.0332</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -4092,10 +4092,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B176" t="n">
-        <v>0.0332</v>
+        <v>0.0233</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -4115,10 +4115,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B177" t="n">
-        <v>0.0233</v>
+        <v>0.0211</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -4138,10 +4138,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B178" t="n">
-        <v>0.0211</v>
+        <v>0.0218</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B179" t="n">
-        <v>0.0218</v>
+        <v>0.0308</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -4184,10 +4184,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B180" t="n">
-        <v>0.0308</v>
+        <v>0.0428</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -4207,10 +4207,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B181" t="n">
-        <v>0.0428</v>
+        <v>0.0463</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -4230,10 +4230,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B182" t="n">
-        <v>0.0463</v>
+        <v>0.0123</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -4253,10 +4253,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B183" t="n">
-        <v>0.0123</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -4276,10 +4276,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B184" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.0139</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -4299,10 +4299,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B185" t="n">
-        <v>0.0139</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -4315,29 +4315,6 @@
         </is>
       </c>
       <c r="E185" t="inlineStr">
-        <is>
-          <t>decimal_rate_annual_avg</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="n">
-        <v>2012</v>
-      </c>
-      <c r="B186" t="n">
-        <v>0.005699999999999999</v>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>S1603-C</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
         <is>
           <t>decimal_rate_annual_avg</t>
         </is>
@@ -5513,7 +5490,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
     <col width="33" customWidth="1" min="5" max="5"/>
@@ -5578,44 +5555,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SHAIKH_APPENDIX_16_2</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Shaikh, Capitalism (2016), Appendix 16.2 -- Chapter 16 Data Tables (WageProdData, RXRRULCOECD, ProfitRates, DebtIncRatio, HouseholdDebtService)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Anwar Shaikh (author construction from BLS / BEA NIPA / Federal Reserve Z.1 + H.10 + housedebt / IMF IFS / FRED)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>http://www.anwarshaikhecon.org/</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>mixed (indices, decimal rates, ratios, billions USD)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>annual (and quarterly for HouseholdDebtService)</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Copyright OUP; underlying BLS/BEA/Fed/IMF data are public domain or freely redistributable. Reproduced under fair use for replication.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>salvaged xlsx (anwarshaikhecon.org now offline)</t>
-        </is>
-      </c>
+          <t>SHAIKH_APPENDIX_16_PROFITRATES_TBILL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5790,7 +5739,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8">
@@ -5853,7 +5802,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{"S1603-A": {"n": 53, "mae": 0.0, "max_pct_err": 0.0, "div_years": []}, "S1603-B": {"n": 53, "mae": 0.0, "max_pct_err": 0.0, "div_years": []}, "S1603-C": {"n": 19, "mae": 0.0, "max_pct_err": 0.0, "div_years": []}}</t>
+          <t>{"S1603-A": {"n": 52, "mae": 0.0, "max_pct_err": 0.0, "div_years": []}, "S1603-B": {"n": 53, "mae": 0.0, "max_pct_err": 0.0, "div_years": []}, "S1603-C": {"n": 19, "mae": 0.0, "max_pct_err": 0.0, "div_years": []}}</t>
         </is>
       </c>
     </row>
@@ -5865,7 +5814,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-19T00:19:58.109805+00:00</t>
+          <t>2026-07-10T19:12:55.230819+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1603_extenbook.xlsx
+++ b/extenbooks/S1603_extenbook.xlsx
@@ -4332,7 +4332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A196"/>
+  <dimension ref="A1:A211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -4507,7 +4507,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>| **S1603-A** | 1960-2012 | Shaikh Appendix 16.2 — column `US` from `Appendix16_RXRRULCOECD.xlsx` | decimal rate | Salvaged xlsx |</t>
+          <t>| **S1603-A** | 1960-2011 | Shaikh Appendix 16 — column `Interest Rate (3-mo. T-Bill)` from `Appendix16_ProfitRates.xlsx` (= ERP Table 73 / FRED TB3MS) | decimal rate | Salvaged xlsx |</t>
         </is>
       </c>
     </row>
@@ -4675,17 +4675,21 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Direct continuation: book Appendix 16.2 `US` column (1960-2012) -&gt; FRED `TB3MS` annual-avg (2013-2024) via direct splice (same agency / same release).</t>
+          <t>Book Appendix 16 `Interest Rate (3-mo. T-Bill)` column (1960-2011) -&gt; FRED `TB3MS`</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>annual-avg (2012-2024) via direct splice (same instrument / same St. Louis Fed</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>## 5. Year coverage</t>
+          <t>redistribution of the US Treasury 3-month bill).</t>
         </is>
       </c>
     </row>
@@ -4695,262 +4699,274 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>- **Book period**: 1960-2012</t>
+          <t>**P2.6 source correction (F-P2.1-01, 2026-07-10).** S1603-A previously read the `US`</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>- **Extension period**: 2013-2024</t>
+          <t>column of `Appendix16_RXRRULCOECD.xlsx` (1981=0.15911, 2011=0.00300). That column is an</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>- **Total**: 1960-2024</t>
+          <t>OECD-MEI-basis interbank/short rate carrying a positive spread over the T-Bill in *every*</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>year (0.24–2.36pp) and is NOT the instrument the book plots for the US line. The book is</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>## 6. Units</t>
+          <t>explicit (KB `ch16_growth_crises.md` L390-392, L465-466, L479-484): Fig 16.6 and Fig 16.7</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>plot "the 3-month T-Bill interest rate in the United States … 14.03% in 1981 … As of 2011</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>- **S1603 (final)**: percent per annum (annual averages of monthly observations)</t>
+          <t>the US rate stood at 0.0006 (i.e., 0.06%)". The loader now reads Shaikh's own</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>- Book Appendix uses decimal (0.0292 = 2.92%); RSCD converts to percent during processing for axis consistency with FRED. Conversion factor 100 documented in P02.</t>
+          <t>`Appendix16_ProfitRates.xlsx` `Interest Rate (3-mo. T-Bill)` column (1981=0.14029,</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2011=0.00060), reproducing the printed values exactly and splicing continuously to FRED</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>## 7. Caveats</t>
+          <t>TB3MS. Independent anchors `S1603_A_tbill_1981` / `_2011` guard the fix (GREEN).</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>S1603-A now ends 2011 (the T-Bill column has no 2012; Fig 16.7's own range is 1960-2011).</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1. **Bespoke OECD construction.** The book's OECD weighted average is Shaikh-Ragab original work, not an off-the-shelf series. Replication requires multi-country fetch and weighted aggregation. The OECD MEI variant is offered as a low-effort fallback with explicit proxy flag.</t>
+          <t>OECD (S1603-B) and EU (S1603-C) are unchanged (RXRRULCOECD OECD/EU columns).</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2. **gpoaccess.gov ERP URL is DNS-dead.** The original book citation `http://www.gpoaccess.gov/eop/tables10.html` returns DNS failure as of 2026-05-18. The Economic Report of the President has migrated to `https://www.govinfo.gov/app/collection/erp`. RSCD cites govinfo as the live provenance URL; FRED `TB3MS` is the practical extension data source.</t>
-        </is>
-      </c>
+      <c r="A75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3. **Trade-weight vintage decision.** Fed H.10 weights are themselves revised. RSCD uses latest-vintage weights for all years (Phase 4 ratified to avoid weight churn across years). Vintage-as-of methodology is documented as a sensitivity variant.</t>
+          <t>## 5. Year coverage</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>4. **No US proxy.** US rate is directly continued via FRED `TB3MS` which is the same St. Louis Fed redistribution of the US Treasury auction-result 3-month bill rate the book cites via ERP Table 73.</t>
-        </is>
-      </c>
+      <c r="A77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>- **Book period**: 1960-2012</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>## 8. Cross-references</t>
+          <t>- **Extension period**: 2013-2024</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>- **Total**: 1960-2024</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>- **CD legacy ID**: `S098`</t>
-        </is>
-      </c>
+      <c r="A81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>- **CD2 legacy ID**: `S098` (5 subseries A-E)</t>
+          <t>## 6. Units</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>- **Predecessor artifact**: `SalvagedInputs/extension_benchmarks/CD2_v1.3/Series/S098_*`</t>
-        </is>
-      </c>
+      <c r="A83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>- **Book reference**: Shaikh (2016), Ch. 16, p. 733 (Fig 16.7); Appendix 16.1 p. 899</t>
+          <t>- **S1603 (final)**: percent per annum (annual averages of monthly observations)</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>- Book Appendix uses decimal (0.0292 = 2.92%); RSCD converts to percent during processing for axis consistency with FRED. Conversion factor 100 documented in P02.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>## 9. Validation expectation</t>
-        </is>
-      </c>
+      <c r="A86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>## 7. Caveats</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>- **Tolerance**: ±1.0% per year on S1603-A (US) and S1603-B (OECD) against Appendix 16.2 columns over 1960-2012.</t>
-        </is>
-      </c>
+      <c r="A88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>- **Variant divergence (expected)**: `S1603_oecd_mei` may diverge from `S1603_replicated` by 50-100bp in individual years due to basket and weighting differences; this divergence is documented in the validator output, NOT treated as a failure.</t>
+          <t>1. **Bespoke OECD construction.** The book's OECD weighted average is Shaikh-Ragab original work, not an off-the-shelf series. Replication requires multi-country fetch and weighted aggregation. The OECD MEI variant is offered as a low-effort fallback with explicit proxy flag.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>2. **gpoaccess.gov ERP URL is DNS-dead.** The original book citation `http://www.gpoaccess.gov/eop/tables10.html` returns DNS failure as of 2026-05-18. The Economic Report of the President has migrated to `https://www.govinfo.gov/app/collection/erp`. RSCD cites govinfo as the live provenance URL; FRED `TB3MS` is the practical extension data source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>3. **Trade-weight vintage decision.** Fed H.10 weights are themselves revised. RSCD uses latest-vintage weights for all years (Phase 4 ratified to avoid weight churn across years). Vintage-as-of methodology is documented as a sensitivity variant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>4. **No US proxy.** US rate is directly continued via FRED `TB3MS` which is the same St. Louis Fed redistribution of the US Treasury auction-result 3-month bill rate the book cites via ERP Table 73.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>## 8. Cross-references</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>- **CD legacy ID**: `S098`</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>- **CD2 legacy ID**: `S098` (5 subseries A-E)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>- **Predecessor artifact**: `SalvagedInputs/extension_benchmarks/CD2_v1.3/Series/S098_*`</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>- **Book reference**: Shaikh (2016), Ch. 16, p. 733 (Fig 16.7); Appendix 16.1 p. 899</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>- **Tolerance**: ±1.0% per year on S1603-A (US) and S1603-B (OECD) against Appendix 16.2 columns over 1960-2012.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>- **Variant divergence (expected)**: `S1603_oecd_mei` may diverge from `S1603_replicated` by 50-100bp in individual years due to basket and weighting differences; this divergence is documented in the validator output, NOT treated as a failure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
           <t>- **Expected MAE on book period**: &lt; 0.5% for both US and OECD-book columns since we read them directly.</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="4">
+    <row r="108">
+      <c r="A108" s="4">
         <f>== EPR: S1603_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t># S1603 — Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>**Series**: S1603 — US and OECD Short-Term Interest Rates</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>**Construction classification**: `composite`</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>**Extension method**: dual-variant — (1) S1603_replicated re-aggregates Fed H.10 × IMF IFS each run; (2) S1603_oecd_mei reads OECD MEI IRSTCI01 directly (proxy:true)</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>**Authored**: 2026-05-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>**Author**: opus-subagent-ch16-fanout</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>## 1. Why this series is extendable</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>`time_series`. The US 3-month T-bill (`TB3MS`) is continuously published. The OECD weighted aggregate is reconstructable from the same underlying inputs (Fed H.10 trade weights + IMF IFS country rates). An off-the-shelf approximation (OECD MEI) is available for users who don't need book-fidelity replication.</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr"/>
-    </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>## 2. Construction classification</t>
+          <t># S1603 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
@@ -4960,90 +4976,82 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>`composite` — multiple country rates weighted into one aggregate. The Anu lazy-splice rule applies: the extension must recompute the weighted aggregate from extended component data, not naively splice a growth rate onto the book-period level. This is what `S1603_replicated` does.</t>
+          <t>**Series**: S1603 — US and OECD Short-Term Interest Rates</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr"/>
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>**Phase**: 6 (Extension)</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>## 3. Method — Variant 1: S1603_replicated (canonical)</t>
+          <t>**Construction classification**: `composite`</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr"/>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>**Extension method**: dual-variant — (1) S1603_replicated re-aggregates Fed H.10 × IMF IFS each run; (2) S1603_oecd_mei reads OECD MEI IRSTCI01 directly (proxy:true)</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>**Authored**: 2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>INPUTS</t>
+          <t>**Author**: opus-subagent-ch16-fanout</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Fed H.10 weights:  https://www.federalreserve.gov/releases/h10/Weights/</t>
-        </is>
-      </c>
+      <c r="A117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">    -&gt; table_a.csv (broad index trade weights, latest vintage)</t>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  IMF IFS country money market rates:</t>
-        </is>
-      </c>
+      <c r="A119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">    -&gt; https://data.imf.org/IFS (FM_PA / FIMM_PA / Money Market Rate)</t>
+          <t>## 1. Why this series is extendable</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Shaikh OECD basket (per CD2 S098 country list):</t>
-        </is>
-      </c>
+      <c r="A121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">    USA omitted (US is plotted separately), plus</t>
+          <t>`time_series`. The US 3-month T-bill (`TB3MS`) is continuously published. The OECD weighted aggregate is reconstructable from the same underlying inputs (Fed H.10 trade weights + IMF IFS country rates). An off-the-shelf approximation (OECD MEI) is available for users who don't need book-fidelity replication.</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    DEU, FRA, GBR, JPN, ITA, CAN, AUS, CHE, SWE, NLD, BEL, KOR, MEX, ESP,</t>
-        </is>
-      </c>
+      <c r="A123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">    plus additional partners weighted into Fed H.10 broad index.</t>
+          <t>## 2. Construction classification</t>
         </is>
       </c>
     </row>
@@ -5053,90 +5061,90 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AGGREGATION</t>
+          <t>`composite` — multiple country rates weighted into one aggregate. The Anu lazy-splice rule applies: the extension must recompute the weighted aggregate from extended component data, not naively splice a growth rate onto the book-period level. This is what `S1603_replicated` does.</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  For year t in [1960, 2024]:</t>
-        </is>
-      </c>
+      <c r="A127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">    weights w_{c,t}  = latest-vintage Fed H.10 weight for c (annual avg of monthly)</t>
+          <t>## 3. Method — Variant 1: S1603_replicated (canonical)</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    rates   i_{c,t}  = IMF IFS Money Market Rate for c (annual avg of monthly)</t>
-        </is>
-      </c>
+      <c r="A129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ioecd_t          = sum_c (w_{c,t} * i_{c,t}) / sum_c (w_{c,t})</t>
+          <t>```</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr"/>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>INPUTS</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SPLICE</t>
+          <t xml:space="preserve">  Fed H.10 weights:  https://www.federalreserve.gov/releases/h10/Weights/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">  S1603-B_book        = Appendix 16.2 OECD column (1960-2012)</t>
+          <t xml:space="preserve">    -&gt; table_a.csv (broad index trade weights, latest vintage)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">  S1603-F_replicated  = computed ioecd_t from Fed H.10 + IMF IFS (1960-2024)</t>
+          <t xml:space="preserve">  IMF IFS country money market rates:</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cross-check 1960-2012: replicated should match book within +/- 50bp (validates rebuild)</t>
+          <t xml:space="preserve">    -&gt; https://data.imf.org/IFS (FM_PA / FIMM_PA / Money Market Rate)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Final published S1603-B_extended: book 1960-2012 || replicated 2013-2024</t>
+          <t xml:space="preserve">  Shaikh OECD basket (per CD2 S098 country list):</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">    USA omitted (US is plotted separately), plus</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr"/>
+      <c r="A138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    DEU, FRA, GBR, JPN, ITA, CAN, AUS, CHE, SWE, NLD, BEL, KOR, MEX, ESP,</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>## 4. Method — Variant 2: S1603_oecd_mei (proxy:true, low-effort)</t>
+          <t xml:space="preserve">    plus additional partners weighted into Fed H.10 broad index.</t>
         </is>
       </c>
     </row>
@@ -5146,99 +5154,95 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>AGGREGATION</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>INPUTS</t>
+          <t xml:space="preserve">  For year t in [1960, 2024]:</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">  OECD MEI:  https://data-explorer.oecd.org/  -&gt;  Subject = IRSTCI01 (Short-term interest rates)</t>
+          <t xml:space="preserve">    weights w_{c,t}  = latest-vintage Fed H.10 weight for c (annual avg of monthly)</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">             Frequency = M, aggregated to annual avg</t>
+          <t xml:space="preserve">    rates   i_{c,t}  = IMF IFS Money Market Rate for c (annual avg of monthly)</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr"/>
+      <c r="A145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ioecd_t          = sum_c (w_{c,t} * i_{c,t}) / sum_c (w_{c,t})</t>
+        </is>
+      </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>S1603-E[t] = OECD_IRSTCI01[t]  for t in [1960, 2024]</t>
-        </is>
-      </c>
+      <c r="A146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr"/>
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>SPLICE</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CONCEPT MATCH JUSTIFICATION</t>
+          <t xml:space="preserve">  S1603-B_book        = Appendix 16.2 OECD column (1960-2012)</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Both S1603-F (replicated) and S1603-E (OECD MEI) measure trade-weighted OECD</t>
+          <t xml:space="preserve">  S1603-F_replicated  = computed ioecd_t from Fed H.10 + IMF IFS (1960-2024)</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">  short-term interest rates. They differ in:</t>
+          <t xml:space="preserve">  Cross-check 1960-2012: replicated should match book within +/- 50bp (validates rebuild)</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">    (a) weighting base: Fed H.10 trade weights (Shaikh-Ragab) vs OECD GDP-PPP weights</t>
+          <t xml:space="preserve">  Final published S1603-B_extended: book 1960-2012 || replicated 2013-2024</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">    (b) basket composition: minor differences in country list and tier coverage</t>
+          <t>```</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  The two should track within +/- 100bp in any given year. OECD MEI is offered</t>
-        </is>
-      </c>
+      <c r="A153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">  as a low-friction alternative for users who do not require book-fidelity</t>
+          <t>## 4. Method — Variant 2: S1603_oecd_mei (proxy:true, low-effort)</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  replication. Flagged `proxy: true` with explicit CMJ.</t>
-        </is>
-      </c>
+      <c r="A155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5248,228 +5252,325 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr"/>
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>INPUTS</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>## 5. US component extension</t>
+          <t xml:space="preserve">  OECD MEI:  https://data-explorer.oecd.org/  -&gt;  Subject = IRSTCI01 (Short-term interest rates)</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr"/>
+      <c r="A159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             Frequency = M, aggregated to annual avg</t>
+        </is>
+      </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="A160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>S1603-A_book     = Appendix 16.2 US column (1960-2012)</t>
+          <t>S1603-E[t] = OECD_IRSTCI01[t]  for t in [1960, 2024]</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>S1603-D[t]       = FRED TB3MS annual-avg[t]  for t in [2013, 2024]</t>
-        </is>
-      </c>
+      <c r="A162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>S1603-A_extended = book 1960-2012 || FRED 2013-2024 (direct splice, same series)</t>
+          <t>CONCEPT MATCH JUSTIFICATION</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">  Both S1603-F (replicated) and S1603-E (OECD MEI) measure trade-weighted OECD</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr"/>
+      <c r="A165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  short-term interest rates. They differ in:</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Same-agency direct splice; no proxy concern.</t>
+          <t xml:space="preserve">    (a) weighting base: Fed H.10 trade weights (Shaikh-Ragab) vs OECD GDP-PPP weights</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr"/>
+      <c r="A167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (b) basket composition: minor differences in country list and tier coverage</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>## 6. Proxies</t>
+          <t xml:space="preserve">  The two should track within +/- 100bp in any given year. OECD MEI is offered</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr"/>
+      <c r="A169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  as a low-friction alternative for users who do not require book-fidelity</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>- **S1603_oecd_mei** is flagged `proxy: true` with CMJ above.</t>
+          <t xml:space="preserve">  replication. Flagged `proxy: true` with explicit CMJ.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>- **S1603_replicated** is NOT a proxy — it rebuilds Shaikh-Ragab's exact methodology using the original inputs.</t>
+          <t>```</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>- US (TB3MS): same series, same agency, direct continuation. `proxy: false`.</t>
-        </is>
-      </c>
+      <c r="A172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr"/>
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>## 5. US component extension</t>
+        </is>
+      </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>## 7. Synthetic data</t>
-        </is>
-      </c>
+      <c r="A174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr"/>
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>**None permitted.** If IMF IFS or Fed H.10 weights are unavailable for a country/year, that country is dropped from the weighted sum for that year, the remaining weights re-normalized, and the diagnostic flags the country/year omission. No fabricated values, no carry-forward.</t>
+          <t>S1603-A_book     = Appendix 16.2 US column (1960-2012)</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr"/>
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>S1603-D[t]       = FRED TB3MS annual-avg[t]  for t in [2013, 2024]</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>## 8. Failure modes &amp; graceful degradation</t>
+          <t>S1603-A_extended = book 1960-2012 || FRED 2013-2024 (direct splice, same series)</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr"/>
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>| Failure | Detection | Action |</t>
-        </is>
-      </c>
+      <c r="A180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>|---|---|---|</t>
+          <t>Same-agency direct splice; no proxy concern.</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>| FRED_API_KEY missing | startup | US extension marked unavailable; book US 1960-2012 published only |</t>
-        </is>
-      </c>
+      <c r="A182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>| Fed H.10 weights CSV unreachable | HTTP non-200 | Replicated variant marked unavailable; OECD MEI variant remains valid |</t>
+          <t>## 6. Proxies</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>| IMF IFS country gap | per-country fetch | Drop country from sum that year; re-normalize; log in diagnostics |</t>
-        </is>
-      </c>
+      <c r="A184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>| OECD MEI endpoint reorganized | HTTP non-200 | OECD MEI variant marked unavailable; replicated variant remains canonical |</t>
+          <t>- **S1603_oecd_mei** is flagged `proxy: true` with CMJ above.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>| Both variants fail | composite check | Book period 1960-2012 published; extension marked `data_unavailable` |</t>
+          <t>- **S1603_replicated** is NOT a proxy — it rebuilds Shaikh-Ragab's exact methodology using the original inputs.</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr"/>
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>- US (TB3MS): same series, same agency, direct continuation. `proxy: false`.</t>
+        </is>
+      </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>## 9. CD2 divergence</t>
-        </is>
-      </c>
+      <c r="A188" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr"/>
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>## 7. Synthetic data</t>
+        </is>
+      </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>CD2's `S098` had 5 subseries (A OECD annual, B US from Appendix 6.8, C OECD MEI alt, D OECD/EU ratio, E combined fill-in). RSCD S1603 retains A (book OECD), B (book US), C (book EU), plus three new extension subseries (D US-TB3MS, E OECD-MEI, F replicated). The fill-in logic in CD2's S098-E is absorbed into the replicated variant's per-country drop-and-renormalize behavior.</t>
-        </is>
-      </c>
+      <c r="A190" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr"/>
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>**None permitted.** If IMF IFS or Fed H.10 weights are unavailable for a country/year, that country is dropped from the weighted sum for that year, the remaining weights re-normalized, and the diagnostic flags the country/year omission. No fabricated values, no carry-forward.</t>
+        </is>
+      </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>## 10. Splice diagnostics (V03)</t>
-        </is>
-      </c>
+      <c r="A192" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr"/>
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>## 8. Failure modes &amp; graceful degradation</t>
+        </is>
+      </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>- Cross-check: replicated 1960-2012 vs book OECD column — MAE expected &lt; 50bp</t>
-        </is>
-      </c>
+      <c r="A194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>- Cross-check: OECD MEI 1960-2012 vs book OECD column — MAE expected &lt; 100bp (proxy divergence is informational)</t>
+          <t>| Failure | Detection | Action |</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
+        <is>
+          <t>|---|---|---|</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>| FRED_API_KEY missing | startup | US extension marked unavailable; book US 1960-2012 published only |</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>| Fed H.10 weights CSV unreachable | HTTP non-200 | Replicated variant marked unavailable; OECD MEI variant remains valid |</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>| IMF IFS country gap | per-country fetch | Drop country from sum that year; re-normalize; log in diagnostics |</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>| OECD MEI endpoint reorganized | HTTP non-200 | OECD MEI variant marked unavailable; replicated variant remains canonical |</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>| Both variants fail | composite check | Book period 1960-2012 published; extension marked `data_unavailable` |</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>## 9. CD2 divergence</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>CD2's `S098` had 5 subseries (A OECD annual, B US from Appendix 6.8, C OECD MEI alt, D OECD/EU ratio, E combined fill-in). RSCD S1603 retains A (book OECD), B (book US), C (book EU), plus three new extension subseries (D US-TB3MS, E OECD-MEI, F replicated). The fill-in logic in CD2's S098-E is absorbed into the replicated variant's per-country drop-and-renormalize behavior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>## 10. Splice diagnostics (V03)</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>- Cross-check: replicated 1960-2012 vs book OECD column — MAE expected &lt; 50bp</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>- Cross-check: OECD MEI 1960-2012 vs book OECD column — MAE expected &lt; 100bp (proxy divergence is informational)</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
         <is>
           <t>- US splice continuity at 2012: TB3MS[2012] vs book US[2012] — should match within 10bp</t>
         </is>
@@ -5814,7 +5915,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-10T19:12:55.230819+00:00</t>
+          <t>2026-07-11T03:44:23.701810+00:00</t>
         </is>
       </c>
     </row>
@@ -5829,11 +5930,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5856,6 +5957,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_16_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "KB-verified: figure 16.7 caption and in-text description (p.733) match; appendix sourcing (Fed H.10 trade weights, IMF IFS) confirmed; verbatim quotes match.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1603_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1603_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Latest-vintage Fed H.10 trade weights ratified for all years; vintage-as-of methodology documented as sensitivity variant. | P2.6 F-P2.1-01: S1603-A US source corrected to the 3-mo T-Bill (ProfitRates appendix); was RXRRULCOECD US (OECD-MEI interbank).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>decimal_rate_annual_avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
